--- a/FoodApp_TestCases.xlsx
+++ b/FoodApp_TestCases.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5047EBA7-0D82-4E5F-873A-C6D202CF1AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AFDF078-13A5-42D4-8F6A-D1692316BEB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{FFC57FE3-C260-4225-A4E9-F1F8501EFE6F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{FFC57FE3-C260-4225-A4E9-F1F8501EFE6F}"/>
   </bookViews>
   <sheets>
     <sheet name="USER REGISTRATION" sheetId="1" r:id="rId1"/>
     <sheet name="USER_LOGIN" sheetId="2" r:id="rId2"/>
     <sheet name="HOME_PAGE" sheetId="3" r:id="rId3"/>
     <sheet name="PRODUCT_PAGE" sheetId="4" r:id="rId4"/>
+    <sheet name="SYSTEM_SCENARIO" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2355" uniqueCount="1275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2448" uniqueCount="1338">
   <si>
     <t>APPLICATION NAME</t>
   </si>
@@ -3020,6 +3021,9 @@
   </si>
   <si>
     <t>INVALID DATA</t>
+  </si>
+  <si>
+    <t>PASSWORD_UPDATE</t>
   </si>
   <si>
     <t>FOA_HP_001</t>
@@ -3915,12 +3919,235 @@
   <si>
     <t>SOCIAL_MEDIA_DUPLICATE_MSG</t>
   </si>
+  <si>
+    <t>FOA_SYSTEM_001</t>
+  </si>
+  <si>
+    <t>REG_TO_DASHBOARD</t>
+  </si>
+  <si>
+    <t>SYSTEM</t>
+  </si>
+  <si>
+    <t>TO CHECK NEW USER REGISTRATION TO DASHBOARD FLOW</t>
+  </si>
+  <si>
+    <t>CLICK ON THE APP --&gt;
+OPEN REGISTRATION PAGE --&gt;
+ENTER DETAILS &amp; CHECK TERMS --&gt;
+ENTER OTP --&gt;
+REDIRECT TO LOGIN --&gt;
+ENTER CREDENTIALS</t>
+  </si>
+  <si>
+    <t>VALID REGISTRATION AND LOGIN DETAILS</t>
+  </si>
+  <si>
+    <t>ACCOUNT CREATED SUCCESSFULLY, SESSION CREATED, USER REDIRECTED TO HOME PAGE DASHBOARD</t>
+  </si>
+  <si>
+    <t>FOA_SYSTEM_002</t>
+  </si>
+  <si>
+    <t>INVALID_REG_LOGIN</t>
+  </si>
+  <si>
+    <t>TO CHECK INVALID REGISTRATION AND LOGIN ATTEMPT</t>
+  </si>
+  <si>
+    <t>CLICK ON THE APP --&gt;
+OPEN REGISTRATION PAGE --&gt;
+ENTER INVALID NAME/DUPLICATE EMAIL --&gt;
+TRY LOGIN WITH UNREGISTERED DETAILS</t>
+  </si>
+  <si>
+    <t>INVALID OR UNREGISTERED DETAILS</t>
+  </si>
+  <si>
+    <t>INLINE ERROR DISPLAYED, REGISTRATION HALTED. LOGIN DISPLAYS "EMAIL/MOBILE NOT REGISTERED"</t>
+  </si>
+  <si>
+    <t>FOA_SYSTEM_003</t>
+  </si>
+  <si>
+    <t>LOGIN_TO_PROFILE_UPDATE</t>
+  </si>
+  <si>
+    <t>TO CHECK LOGIN TO PROFILE UPDATE FLOW</t>
+  </si>
+  <si>
+    <t>CLICK ON THE APP --&gt;
+LOGIN TO HOME PAGE --&gt;
+CLICK PROFILE ICON --&gt;
+SELECT MY PROFILE --&gt;
+UPDATE DETAILS &amp; ADDRESS --&gt;
+CLICK SAVE</t>
+  </si>
+  <si>
+    <t>VALID LOGIN AND PROFILE UPDATE DETAILS</t>
+  </si>
+  <si>
+    <t>SYSTEM VALIDATES DETAILS, SUCCESS MESSAGE DISPLAYED, PROFILE SAVED</t>
+  </si>
+  <si>
+    <t>FOA_SYSTEM_004</t>
+  </si>
+  <si>
+    <t>TO CHECK PASSWORD UPDATE FLOW</t>
+  </si>
+  <si>
+    <t>CLICK ON THE APP --&gt;
+LOGIN TO HOME PAGE --&gt;
+CLICK PROFILE ICON --&gt;
+SELECT MY PROFILE --&gt;
+OPEN CHANGE PASSWORD --&gt;
+ENTER CURRENT &amp; NEW PASSWORD --&gt;
+CLICK UPDATE</t>
+  </si>
+  <si>
+    <t>VALID CURRENT AND NEW PASSWORDS</t>
+  </si>
+  <si>
+    <t>SYSTEM VALIDATES PASSWORDS, SUCCESS MESSAGE "PASSWORD UPDATED SUCCESSFULLY" DISPLAYED</t>
+  </si>
+  <si>
+    <t>FOA_SYSTEM_005</t>
+  </si>
+  <si>
+    <t>SEARCH_TO_PDP</t>
+  </si>
+  <si>
+    <t>TO CHECK SEARCH TO PRODUCT DISPLAY FLOW</t>
+  </si>
+  <si>
+    <t>CLICK ON THE APP --&gt;
+LOGIN TO HOME PAGE --&gt;
+ENTER SEARCH TERM IN SEARCH BAR --&gt;
+SELECT FROM AUTO-SUGGESTIONS</t>
+  </si>
+  <si>
+    <t>SEARCH TERM ≥ 2 CHARACTERS</t>
+  </si>
+  <si>
+    <t>NAVIGATED TO PDP, CARDS SHOWN WITH IMAGE, NAME, DESC, PRICE, RATING, ADD TO CART BUTTON</t>
+  </si>
+  <si>
+    <t>FOA_SYSTEM_006</t>
+  </si>
+  <si>
+    <t>OFFER_TO_PDP</t>
+  </si>
+  <si>
+    <t>TO CHECK OFFER CARD TO PRODUCT DISPLAY FLOW</t>
+  </si>
+  <si>
+    <t>CLICK ON THE APP --&gt;
+LOGIN TO HOME PAGE --&gt;
+CLICK ON ANY OFFER CARD</t>
+  </si>
+  <si>
+    <t>NAVIGATED TO PDP FILTERED BY OFFER, PRODUCTS SHOW DISCOUNTED PRICE AND STRIKETHROUGH ORIGINAL PRICE</t>
+  </si>
+  <si>
+    <t>FOA_SYSTEM_007</t>
+  </si>
+  <si>
+    <t>PDP_TO_CART</t>
+  </si>
+  <si>
+    <t>TO CHECK PRODUCT ADD TO CART FLOW</t>
+  </si>
+  <si>
+    <t>CLICK ON THE APP --&gt;
+NAVIGATE TO PDP --&gt;
+CLICK ADD TO CART --&gt;
+USE QUANTITY SELECTOR (+/-) --&gt;
+CLICK CART ICON</t>
+  </si>
+  <si>
+    <t>CLICK ADD, +, -, AND CART ICON</t>
+  </si>
+  <si>
+    <t>CART BADGE UPDATES DYNAMICALLY, ITEM REMOVED IF QTY=0, NAVIGATED TO CART PAGE WITH UPDATED ITEMS</t>
+  </si>
+  <si>
+    <t>FOA_SYSTEM_008</t>
+  </si>
+  <si>
+    <t>PROD_DETAIL_TO_CART</t>
+  </si>
+  <si>
+    <t>TO CHECK PRODUCT DETAIL TO CART FLOW</t>
+  </si>
+  <si>
+    <t>CLICK ON THE APP --&gt;
+NAVIGATE TO PDP --&gt;
+CLICK PRODUCT CARD --&gt;
+CLICK ADD TO CART IN DETAIL VIEW --&gt;
+CLICK CART ICON</t>
+  </si>
+  <si>
+    <t>CLICK PRODUCT CARD AND ADD TO CART</t>
+  </si>
+  <si>
+    <t>DETAIL VIEW OPENS WITH FULL INFO, ITEM ADDED, BADGE UPDATES, NAVIGATED TO CART PAGE</t>
+  </si>
+  <si>
+    <t>FOA_SYSTEM_009</t>
+  </si>
+  <si>
+    <t>SESSION_EXPIRY</t>
+  </si>
+  <si>
+    <t>TO CHECK SESSION EXPIRY FLOW</t>
+  </si>
+  <si>
+    <t>CLICK ON THE APP --&gt;
+LOGIN TO HOME PAGE --&gt;
+WAIT FOR SESSION TIMEOUT --&gt;
+PERFORM ANY ACTION</t>
+  </si>
+  <si>
+    <t>ACTION AFTER SESSION TIMEOUT</t>
+  </si>
+  <si>
+    <t>SYSTEM REDIRECTS USER TO LOGIN PAGE</t>
+  </si>
+  <si>
+    <t>FOA_SYSTEM_010</t>
+  </si>
+  <si>
+    <t>SOCIAL_MEDIA_LOGIN</t>
+  </si>
+  <si>
+    <t>TO CHECK SOCIAL MEDIA LOGIN FLOW</t>
+  </si>
+  <si>
+    <t>CLICK ON THE APP --&gt;
+SELECT GOOGLE/FACEBOOK LOGIN --&gt;
+AUTHENTICATE</t>
+  </si>
+  <si>
+    <t>VALID SOCIAL CREDENTIALS</t>
+  </si>
+  <si>
+    <t>PROFILE CREATED AUTOMATICALLY, REDIRECTED TO HOME PAGE (OR "ACCOUNT ALREADY EXISTS" IF LINKED)</t>
+  </si>
+  <si>
+    <t>FOOD ORDERING APPLICATION [FOA]</t>
+  </si>
+  <si>
+    <t>FOOD ORDERING APPLICATION SHOULD LOADS</t>
+  </si>
+  <si>
+    <t>VERIFY THE WHOLE FOOD APPLICATION WORK PROPERLY</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4039,6 +4266,19 @@
       <color rgb="FF1F1F1F"/>
       <name val="Google Sans Text"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -4095,7 +4335,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
@@ -4181,6 +4421,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4188,6 +4429,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -4648,7 +4898,7 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -5597,7 +5847,7 @@
         <v>92</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="G46" t="s">
         <v>36</v>
@@ -7340,7 +7590,7 @@
         <v>399</v>
       </c>
       <c r="B127" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="C127" t="s">
         <v>443</v>
@@ -7363,7 +7613,7 @@
         <v>403</v>
       </c>
       <c r="B128" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="C128" t="s">
         <v>443</v>
@@ -7386,7 +7636,7 @@
         <v>405</v>
       </c>
       <c r="B129" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="C129" t="s">
         <v>443</v>
@@ -7409,7 +7659,7 @@
         <v>407</v>
       </c>
       <c r="B130" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="C130" t="s">
         <v>443</v>
@@ -7432,7 +7682,7 @@
         <v>410</v>
       </c>
       <c r="B131" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="C131" t="s">
         <v>443</v>
@@ -7455,7 +7705,7 @@
         <v>412</v>
       </c>
       <c r="B132" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="C132" t="s">
         <v>443</v>
@@ -7492,7 +7742,7 @@
         <v>416</v>
       </c>
       <c r="B136" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C136" t="s">
         <v>29</v>
@@ -7515,7 +7765,7 @@
         <v>419</v>
       </c>
       <c r="B137" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="C137" t="s">
         <v>29</v>
@@ -7538,7 +7788,7 @@
         <v>422</v>
       </c>
       <c r="B138" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="C138" t="s">
         <v>29</v>
@@ -7561,7 +7811,7 @@
         <v>425</v>
       </c>
       <c r="B139" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="C139" t="s">
         <v>29</v>
@@ -7584,7 +7834,7 @@
         <v>428</v>
       </c>
       <c r="B140" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="C140" t="s">
         <v>228</v>
@@ -7851,7 +8101,7 @@
         <v>466</v>
       </c>
       <c r="B156" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="C156" t="s">
         <v>443</v>
@@ -7874,7 +8124,7 @@
         <v>718</v>
       </c>
       <c r="B157" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="C157" t="s">
         <v>443</v>
@@ -7897,7 +8147,7 @@
         <v>720</v>
       </c>
       <c r="B158" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="C158" t="s">
         <v>228</v>
@@ -7920,7 +8170,7 @@
         <v>722</v>
       </c>
       <c r="B159" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C159" t="s">
         <v>228</v>
@@ -7943,7 +8193,7 @@
         <v>724</v>
       </c>
       <c r="B160" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C160" t="s">
         <v>315</v>
@@ -7966,7 +8216,7 @@
         <v>725</v>
       </c>
       <c r="B161" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="C161" t="s">
         <v>228</v>
@@ -7989,7 +8239,7 @@
         <v>726</v>
       </c>
       <c r="B162" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="C162" t="s">
         <v>443</v>
@@ -8802,8 +9052,8 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="37" t="s">
-        <v>989</v>
+      <c r="A9" s="38" t="s">
+        <v>990</v>
       </c>
       <c r="B9" t="s">
         <v>561</v>
@@ -8825,8 +9075,8 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="37" t="s">
-        <v>990</v>
+      <c r="A10" s="38" t="s">
+        <v>991</v>
       </c>
       <c r="B10" t="s">
         <v>565</v>
@@ -8848,8 +9098,8 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="37" t="s">
-        <v>991</v>
+      <c r="A11" s="38" t="s">
+        <v>992</v>
       </c>
       <c r="B11" t="s">
         <v>569</v>
@@ -8871,8 +9121,8 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="37" t="s">
-        <v>992</v>
+      <c r="A12" s="38" t="s">
+        <v>993</v>
       </c>
       <c r="B12" t="s">
         <v>573</v>
@@ -8894,8 +9144,8 @@
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="37" t="s">
-        <v>993</v>
+      <c r="A14" s="38" t="s">
+        <v>994</v>
       </c>
       <c r="B14" t="s">
         <v>577</v>
@@ -8917,8 +9167,8 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="37" t="s">
-        <v>994</v>
+      <c r="A15" s="38" t="s">
+        <v>995</v>
       </c>
       <c r="B15" t="s">
         <v>581</v>
@@ -8940,8 +9190,8 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="37" t="s">
-        <v>995</v>
+      <c r="A16" s="38" t="s">
+        <v>996</v>
       </c>
       <c r="B16" t="s">
         <v>584</v>
@@ -8963,8 +9213,8 @@
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="37" t="s">
-        <v>996</v>
+      <c r="A17" s="38" t="s">
+        <v>997</v>
       </c>
       <c r="B17" t="s">
         <v>588</v>
@@ -8986,8 +9236,8 @@
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="37" t="s">
-        <v>997</v>
+      <c r="A18" s="38" t="s">
+        <v>998</v>
       </c>
       <c r="B18" t="s">
         <v>593</v>
@@ -9009,8 +9259,8 @@
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="37" t="s">
-        <v>998</v>
+      <c r="A19" s="38" t="s">
+        <v>999</v>
       </c>
       <c r="B19" t="s">
         <v>597</v>
@@ -9032,8 +9282,8 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="37" t="s">
-        <v>999</v>
+      <c r="A20" s="38" t="s">
+        <v>1000</v>
       </c>
       <c r="B20" t="s">
         <v>602</v>
@@ -9055,8 +9305,8 @@
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="37" t="s">
-        <v>1000</v>
+      <c r="A21" s="38" t="s">
+        <v>1001</v>
       </c>
       <c r="B21" t="s">
         <v>607</v>
@@ -9078,8 +9328,8 @@
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="37" t="s">
-        <v>1001</v>
+      <c r="A23" s="38" t="s">
+        <v>1002</v>
       </c>
       <c r="B23" t="s">
         <v>612</v>
@@ -9101,8 +9351,8 @@
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="37" t="s">
-        <v>1002</v>
+      <c r="A24" s="38" t="s">
+        <v>1003</v>
       </c>
       <c r="B24" t="s">
         <v>614</v>
@@ -9124,8 +9374,8 @@
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="37" t="s">
-        <v>1003</v>
+      <c r="A25" s="38" t="s">
+        <v>1004</v>
       </c>
       <c r="B25" t="s">
         <v>618</v>
@@ -9147,8 +9397,8 @@
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="37" t="s">
-        <v>1004</v>
+      <c r="A26" s="38" t="s">
+        <v>1005</v>
       </c>
       <c r="B26" t="s">
         <v>621</v>
@@ -9170,8 +9420,8 @@
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="37" t="s">
-        <v>1005</v>
+      <c r="A27" s="38" t="s">
+        <v>1006</v>
       </c>
       <c r="B27" t="s">
         <v>623</v>
@@ -9193,8 +9443,8 @@
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="37" t="s">
-        <v>1006</v>
+      <c r="A28" s="38" t="s">
+        <v>1007</v>
       </c>
       <c r="B28" t="s">
         <v>627</v>
@@ -9217,11 +9467,11 @@
     </row>
     <row r="29" spans="1:7" ht="15" thickBot="1"/>
     <row r="30" spans="1:7" ht="15" thickBot="1">
-      <c r="A30" s="37" t="s">
-        <v>1007</v>
+      <c r="A30" s="38" t="s">
+        <v>1008</v>
       </c>
       <c r="B30" s="34" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="C30" s="34" t="s">
         <v>879</v>
@@ -9238,8 +9488,8 @@
       <c r="G30" s="34"/>
     </row>
     <row r="31" spans="1:7" ht="15" thickBot="1">
-      <c r="A31" s="37" t="s">
-        <v>1008</v>
+      <c r="A31" s="38" t="s">
+        <v>1009</v>
       </c>
       <c r="B31" s="34" t="s">
         <v>855</v>
@@ -9261,11 +9511,11 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" thickBot="1">
-      <c r="A32" s="37" t="s">
-        <v>1009</v>
+      <c r="A32" s="38" t="s">
+        <v>1010</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C32" s="34" t="s">
         <v>882</v>
@@ -9284,11 +9534,11 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" thickBot="1">
-      <c r="A33" s="37" t="s">
-        <v>1010</v>
+      <c r="A33" s="38" t="s">
+        <v>1011</v>
       </c>
       <c r="B33" s="34" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="C33" s="34" t="s">
         <v>882</v>
@@ -9307,8 +9557,8 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" thickBot="1">
-      <c r="A34" s="37" t="s">
-        <v>1011</v>
+      <c r="A34" s="38" t="s">
+        <v>1012</v>
       </c>
       <c r="B34" s="34" t="s">
         <v>856</v>
@@ -9330,11 +9580,11 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" thickBot="1">
-      <c r="A35" s="37" t="s">
-        <v>1012</v>
+      <c r="A35" s="38" t="s">
+        <v>1013</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C35" s="34" t="s">
         <v>882</v>
@@ -9353,11 +9603,11 @@
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" thickBot="1">
-      <c r="A36" s="37" t="s">
-        <v>1013</v>
+      <c r="A36" s="38" t="s">
+        <v>1014</v>
       </c>
       <c r="B36" s="34" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C36" s="34" t="s">
         <v>882</v>
@@ -9376,11 +9626,11 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" thickBot="1">
-      <c r="A37" s="37" t="s">
-        <v>1014</v>
+      <c r="A37" s="38" t="s">
+        <v>1015</v>
       </c>
       <c r="B37" s="34" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="C37" s="34" t="s">
         <v>882</v>
@@ -9399,11 +9649,11 @@
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" thickBot="1">
-      <c r="A38" s="37" t="s">
-        <v>1015</v>
+      <c r="A38" s="38" t="s">
+        <v>1016</v>
       </c>
       <c r="B38" s="34" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="C38" s="34" t="s">
         <v>882</v>
@@ -9422,11 +9672,11 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" thickBot="1">
-      <c r="A39" s="37" t="s">
-        <v>1016</v>
+      <c r="A39" s="38" t="s">
+        <v>1017</v>
       </c>
       <c r="B39" s="34" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="C39" s="34" t="s">
         <v>882</v>
@@ -9445,11 +9695,11 @@
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" thickBot="1">
-      <c r="A40" s="37" t="s">
-        <v>1017</v>
+      <c r="A40" s="38" t="s">
+        <v>1018</v>
       </c>
       <c r="B40" s="34" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C40" s="34" t="s">
         <v>882</v>
@@ -9466,11 +9716,11 @@
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickBot="1">
-      <c r="A41" s="37" t="s">
-        <v>1018</v>
+      <c r="A41" s="38" t="s">
+        <v>1019</v>
       </c>
       <c r="B41" s="34" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="C41" s="34" t="s">
         <v>882</v>
@@ -9489,11 +9739,11 @@
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" thickBot="1">
-      <c r="A42" s="37" t="s">
-        <v>1019</v>
+      <c r="A42" s="38" t="s">
+        <v>1020</v>
       </c>
       <c r="B42" s="34" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="C42" s="34" t="s">
         <v>882</v>
@@ -9512,11 +9762,11 @@
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" thickBot="1">
-      <c r="A43" s="37" t="s">
-        <v>1020</v>
+      <c r="A43" s="38" t="s">
+        <v>1021</v>
       </c>
       <c r="B43" s="34" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="C43" s="34" t="s">
         <v>882</v>
@@ -9535,11 +9785,11 @@
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" thickBot="1">
-      <c r="A44" s="37" t="s">
-        <v>1021</v>
+      <c r="A44" s="38" t="s">
+        <v>1022</v>
       </c>
       <c r="B44" s="34" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="C44" s="34" t="s">
         <v>882</v>
@@ -9558,11 +9808,11 @@
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" thickBot="1">
-      <c r="A45" s="37" t="s">
-        <v>1022</v>
+      <c r="A45" s="38" t="s">
+        <v>1023</v>
       </c>
       <c r="B45" s="34" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="C45" s="34" t="s">
         <v>882</v>
@@ -9581,11 +9831,11 @@
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" thickBot="1">
-      <c r="A46" s="37" t="s">
-        <v>1023</v>
+      <c r="A46" s="38" t="s">
+        <v>1024</v>
       </c>
       <c r="B46" s="34" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="C46" s="34" t="s">
         <v>882</v>
@@ -9604,11 +9854,11 @@
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" thickBot="1">
-      <c r="A47" s="37" t="s">
-        <v>1024</v>
+      <c r="A47" s="38" t="s">
+        <v>1025</v>
       </c>
       <c r="B47" s="34" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="C47" s="34" t="s">
         <v>882</v>
@@ -9627,11 +9877,11 @@
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" thickBot="1">
-      <c r="A48" s="37" t="s">
-        <v>1025</v>
+      <c r="A48" s="38" t="s">
+        <v>1026</v>
       </c>
       <c r="B48" s="34" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="C48" s="34" t="s">
         <v>882</v>
@@ -9650,11 +9900,11 @@
       </c>
     </row>
     <row r="49" spans="1:7" ht="15" thickBot="1">
-      <c r="A49" s="37" t="s">
-        <v>1026</v>
+      <c r="A49" s="38" t="s">
+        <v>1027</v>
       </c>
       <c r="B49" s="34" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="C49" s="34" t="s">
         <v>882</v>
@@ -9682,11 +9932,11 @@
       <c r="G50" s="34"/>
     </row>
     <row r="51" spans="1:7" ht="15" thickBot="1">
-      <c r="A51" s="37" t="s">
-        <v>1027</v>
+      <c r="A51" s="38" t="s">
+        <v>1028</v>
       </c>
       <c r="B51" s="34" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="C51" s="34" t="s">
         <v>879</v>
@@ -9703,11 +9953,11 @@
       </c>
     </row>
     <row r="52" spans="1:7" ht="15" thickBot="1">
-      <c r="A52" s="37" t="s">
-        <v>1028</v>
+      <c r="A52" s="38" t="s">
+        <v>1029</v>
       </c>
       <c r="B52" s="34" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="C52" s="34" t="s">
         <v>879</v>
@@ -9726,11 +9976,11 @@
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1">
-      <c r="A53" s="37" t="s">
-        <v>1029</v>
+      <c r="A53" s="38" t="s">
+        <v>1030</v>
       </c>
       <c r="B53" s="34" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="C53" s="34" t="s">
         <v>879</v>
@@ -9749,11 +9999,11 @@
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickBot="1">
-      <c r="A54" s="37" t="s">
-        <v>1030</v>
+      <c r="A54" s="38" t="s">
+        <v>1031</v>
       </c>
       <c r="B54" s="34" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="C54" s="34" t="s">
         <v>879</v>
@@ -9772,11 +10022,11 @@
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" thickBot="1">
-      <c r="A55" s="37" t="s">
-        <v>1031</v>
+      <c r="A55" s="38" t="s">
+        <v>1032</v>
       </c>
       <c r="B55" s="34" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="C55" s="34" t="s">
         <v>879</v>
@@ -9795,11 +10045,11 @@
       </c>
     </row>
     <row r="56" spans="1:7" ht="15" thickBot="1">
-      <c r="A56" s="37" t="s">
-        <v>1032</v>
+      <c r="A56" s="38" t="s">
+        <v>1033</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="C56" s="34" t="s">
         <v>879</v>
@@ -9818,11 +10068,11 @@
       </c>
     </row>
     <row r="57" spans="1:7" ht="15" thickBot="1">
-      <c r="A57" s="37" t="s">
-        <v>1033</v>
+      <c r="A57" s="38" t="s">
+        <v>1034</v>
       </c>
       <c r="B57" s="34" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="C57" s="34" t="s">
         <v>879</v>
@@ -9841,11 +10091,11 @@
       </c>
     </row>
     <row r="58" spans="1:7" ht="15" thickBot="1">
-      <c r="A58" s="37" t="s">
-        <v>1034</v>
+      <c r="A58" s="38" t="s">
+        <v>1035</v>
       </c>
       <c r="B58" s="34" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="C58" s="34" t="s">
         <v>879</v>
@@ -9864,11 +10114,11 @@
       </c>
     </row>
     <row r="59" spans="1:7" ht="15" thickBot="1">
-      <c r="A59" s="37" t="s">
-        <v>1035</v>
+      <c r="A59" s="38" t="s">
+        <v>1036</v>
       </c>
       <c r="B59" s="34" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="C59" s="34" t="s">
         <v>879</v>
@@ -9887,11 +10137,11 @@
       </c>
     </row>
     <row r="60" spans="1:7" ht="15" thickBot="1">
-      <c r="A60" s="37" t="s">
-        <v>1036</v>
+      <c r="A60" s="38" t="s">
+        <v>1037</v>
       </c>
       <c r="B60" s="34" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="C60" s="34" t="s">
         <v>879</v>
@@ -9908,11 +10158,11 @@
       </c>
     </row>
     <row r="61" spans="1:7" ht="15" thickBot="1">
-      <c r="A61" s="37" t="s">
-        <v>1037</v>
+      <c r="A61" s="38" t="s">
+        <v>1038</v>
       </c>
       <c r="B61" s="34" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="C61" s="34" t="s">
         <v>879</v>
@@ -9931,11 +10181,11 @@
       </c>
     </row>
     <row r="62" spans="1:7" ht="15" thickBot="1">
-      <c r="A62" s="37" t="s">
-        <v>1038</v>
+      <c r="A62" s="38" t="s">
+        <v>1039</v>
       </c>
       <c r="B62" s="34" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="C62" s="34" t="s">
         <v>879</v>
@@ -9954,11 +10204,11 @@
       </c>
     </row>
     <row r="63" spans="1:7" ht="15" thickBot="1">
-      <c r="A63" s="37" t="s">
-        <v>1039</v>
+      <c r="A63" s="38" t="s">
+        <v>1040</v>
       </c>
       <c r="B63" s="34" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="C63" s="34" t="s">
         <v>879</v>
@@ -9977,11 +10227,11 @@
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" thickBot="1">
-      <c r="A64" s="37" t="s">
-        <v>1040</v>
+      <c r="A64" s="38" t="s">
+        <v>1041</v>
       </c>
       <c r="B64" s="34" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="C64" s="34" t="s">
         <v>879</v>
@@ -10000,11 +10250,11 @@
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" thickBot="1">
-      <c r="A65" s="37" t="s">
-        <v>1041</v>
+      <c r="A65" s="38" t="s">
+        <v>1042</v>
       </c>
       <c r="B65" s="34" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="C65" s="34" t="s">
         <v>879</v>
@@ -10023,11 +10273,11 @@
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1">
-      <c r="A66" s="37" t="s">
-        <v>1042</v>
+      <c r="A66" s="38" t="s">
+        <v>1043</v>
       </c>
       <c r="B66" s="34" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="C66" s="34" t="s">
         <v>879</v>
@@ -10046,11 +10296,11 @@
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickBot="1">
-      <c r="A67" s="37" t="s">
-        <v>1043</v>
+      <c r="A67" s="38" t="s">
+        <v>1044</v>
       </c>
       <c r="B67" s="34" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="C67" s="34" t="s">
         <v>879</v>
@@ -10069,11 +10319,11 @@
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" thickBot="1">
-      <c r="A68" s="37" t="s">
-        <v>1044</v>
+      <c r="A68" s="38" t="s">
+        <v>1045</v>
       </c>
       <c r="B68" s="34" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="C68" s="34" t="s">
         <v>879</v>
@@ -10092,11 +10342,11 @@
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" thickBot="1">
-      <c r="A69" s="37" t="s">
-        <v>1045</v>
+      <c r="A69" s="38" t="s">
+        <v>1046</v>
       </c>
       <c r="B69" s="34" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="C69" s="34" t="s">
         <v>879</v>
@@ -10124,11 +10374,11 @@
       <c r="G70" s="34"/>
     </row>
     <row r="71" spans="1:7" ht="15" thickBot="1">
-      <c r="A71" s="37" t="s">
-        <v>1046</v>
+      <c r="A71" s="38" t="s">
+        <v>1047</v>
       </c>
       <c r="B71" s="34" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="C71" s="34" t="s">
         <v>879</v>
@@ -10147,11 +10397,11 @@
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" thickBot="1">
-      <c r="A72" s="37" t="s">
-        <v>1047</v>
+      <c r="A72" s="38" t="s">
+        <v>1048</v>
       </c>
       <c r="B72" s="34" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="C72" s="34" t="s">
         <v>879</v>
@@ -10170,11 +10420,11 @@
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" thickBot="1">
-      <c r="A73" s="37" t="s">
-        <v>1048</v>
+      <c r="A73" s="38" t="s">
+        <v>1049</v>
       </c>
       <c r="B73" s="34" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C73" s="34" t="s">
         <v>879</v>
@@ -10191,11 +10441,11 @@
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" thickBot="1">
-      <c r="A74" s="37" t="s">
-        <v>1049</v>
+      <c r="A74" s="38" t="s">
+        <v>1050</v>
       </c>
       <c r="B74" s="34" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="C74" s="34" t="s">
         <v>879</v>
@@ -10214,11 +10464,11 @@
       </c>
     </row>
     <row r="75" spans="1:7" ht="15" thickBot="1">
-      <c r="A75" s="37" t="s">
-        <v>1050</v>
+      <c r="A75" s="38" t="s">
+        <v>1051</v>
       </c>
       <c r="B75" s="34" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="C75" s="34" t="s">
         <v>879</v>
@@ -10237,11 +10487,11 @@
       </c>
     </row>
     <row r="76" spans="1:7" ht="15" thickBot="1">
-      <c r="A76" s="37" t="s">
-        <v>1051</v>
+      <c r="A76" s="38" t="s">
+        <v>1052</v>
       </c>
       <c r="B76" s="34" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="C76" s="34" t="s">
         <v>879</v>
@@ -10260,11 +10510,11 @@
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" thickBot="1">
-      <c r="A77" s="37" t="s">
-        <v>1052</v>
+      <c r="A77" s="38" t="s">
+        <v>1053</v>
       </c>
       <c r="B77" s="34" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="C77" s="34" t="s">
         <v>879</v>
@@ -10281,11 +10531,11 @@
       </c>
     </row>
     <row r="78" spans="1:7" ht="15" thickBot="1">
-      <c r="A78" s="37" t="s">
-        <v>1053</v>
+      <c r="A78" s="38" t="s">
+        <v>1054</v>
       </c>
       <c r="B78" s="34" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="C78" s="34" t="s">
         <v>879</v>
@@ -10304,11 +10554,11 @@
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1">
-      <c r="A79" s="37" t="s">
-        <v>1054</v>
+      <c r="A79" s="38" t="s">
+        <v>1055</v>
       </c>
       <c r="B79" s="34" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C79" s="34" t="s">
         <v>879</v>
@@ -10327,11 +10577,11 @@
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" thickBot="1">
-      <c r="A80" s="37" t="s">
-        <v>1055</v>
+      <c r="A80" s="38" t="s">
+        <v>1056</v>
       </c>
       <c r="B80" s="34" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="C80" s="34" t="s">
         <v>879</v>
@@ -10350,11 +10600,11 @@
       </c>
     </row>
     <row r="81" spans="1:7" ht="15" thickBot="1">
-      <c r="A81" s="37" t="s">
-        <v>1056</v>
+      <c r="A81" s="38" t="s">
+        <v>1057</v>
       </c>
       <c r="B81" s="34" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="C81" s="34" t="s">
         <v>879</v>
@@ -10373,11 +10623,11 @@
       </c>
     </row>
     <row r="82" spans="1:7" ht="15" thickBot="1">
-      <c r="A82" s="37" t="s">
-        <v>1057</v>
+      <c r="A82" s="38" t="s">
+        <v>1058</v>
       </c>
       <c r="B82" s="34" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="C82" s="34" t="s">
         <v>879</v>
@@ -10396,11 +10646,11 @@
       </c>
     </row>
     <row r="83" spans="1:7" ht="15" thickBot="1">
-      <c r="A83" s="37" t="s">
-        <v>1058</v>
+      <c r="A83" s="38" t="s">
+        <v>1059</v>
       </c>
       <c r="B83" s="34" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="C83" s="34" t="s">
         <v>879</v>
@@ -10419,11 +10669,11 @@
       </c>
     </row>
     <row r="84" spans="1:7" ht="15" thickBot="1">
-      <c r="A84" s="37" t="s">
-        <v>1120</v>
+      <c r="A84" s="38" t="s">
+        <v>1121</v>
       </c>
       <c r="B84" s="34" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="C84" s="34" t="s">
         <v>879</v>
@@ -10442,11 +10692,11 @@
       </c>
     </row>
     <row r="85" spans="1:7" ht="15" thickBot="1">
-      <c r="A85" s="37" t="s">
-        <v>1121</v>
+      <c r="A85" s="38" t="s">
+        <v>1122</v>
       </c>
       <c r="B85" s="34" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="C85" s="34" t="s">
         <v>879</v>
@@ -10465,11 +10715,11 @@
       </c>
     </row>
     <row r="86" spans="1:7" ht="15" thickBot="1">
-      <c r="A86" s="37" t="s">
-        <v>1122</v>
+      <c r="A86" s="38" t="s">
+        <v>1123</v>
       </c>
       <c r="B86" s="34" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="C86" s="34" t="s">
         <v>879</v>
@@ -10488,11 +10738,11 @@
       </c>
     </row>
     <row r="87" spans="1:7" ht="15" thickBot="1">
-      <c r="A87" s="37" t="s">
-        <v>1123</v>
+      <c r="A87" s="38" t="s">
+        <v>1124</v>
       </c>
       <c r="B87" s="34" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="C87" s="34" t="s">
         <v>879</v>
@@ -10511,11 +10761,11 @@
       </c>
     </row>
     <row r="88" spans="1:7" ht="15" thickBot="1">
-      <c r="A88" s="37" t="s">
-        <v>1124</v>
+      <c r="A88" s="38" t="s">
+        <v>1125</v>
       </c>
       <c r="B88" s="34" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="C88" s="34" t="s">
         <v>879</v>
@@ -10543,8 +10793,8 @@
       <c r="G89" s="34"/>
     </row>
     <row r="90" spans="1:7" ht="15" thickBot="1">
-      <c r="A90" s="37" t="s">
-        <v>1125</v>
+      <c r="A90" s="38" t="s">
+        <v>1126</v>
       </c>
       <c r="B90" s="34" t="s">
         <v>977</v>
@@ -10564,8 +10814,8 @@
       <c r="G90" s="34"/>
     </row>
     <row r="91" spans="1:7" ht="15" thickBot="1">
-      <c r="A91" s="37" t="s">
-        <v>1126</v>
+      <c r="A91" s="38" t="s">
+        <v>1127</v>
       </c>
       <c r="B91" s="34" t="s">
         <v>977</v>
@@ -10585,8 +10835,8 @@
       <c r="G91" s="34"/>
     </row>
     <row r="92" spans="1:7" ht="15" thickBot="1">
-      <c r="A92" s="37" t="s">
-        <v>1127</v>
+      <c r="A92" s="38" t="s">
+        <v>1128</v>
       </c>
       <c r="B92" s="34" t="s">
         <v>977</v>
@@ -10606,8 +10856,8 @@
       <c r="G92" s="34"/>
     </row>
     <row r="93" spans="1:7" ht="15" thickBot="1">
-      <c r="A93" s="37" t="s">
-        <v>1128</v>
+      <c r="A93" s="38" t="s">
+        <v>1129</v>
       </c>
       <c r="B93" s="34" t="s">
         <v>977</v>
@@ -10636,8 +10886,8 @@
       <c r="G94" s="34"/>
     </row>
     <row r="95" spans="1:7" ht="15" thickBot="1">
-      <c r="A95" s="37" t="s">
-        <v>1129</v>
+      <c r="A95" s="38" t="s">
+        <v>1130</v>
       </c>
       <c r="B95" s="34" t="s">
         <v>983</v>
@@ -10659,8 +10909,8 @@
       </c>
     </row>
     <row r="96" spans="1:7" ht="15" thickBot="1">
-      <c r="A96" s="37" t="s">
-        <v>1130</v>
+      <c r="A96" s="38" t="s">
+        <v>1131</v>
       </c>
       <c r="B96" s="34" t="s">
         <v>983</v>
@@ -10682,8 +10932,8 @@
       </c>
     </row>
     <row r="97" spans="1:7" ht="15" thickBot="1">
-      <c r="A97" s="37" t="s">
-        <v>1131</v>
+      <c r="A97" s="38" t="s">
+        <v>1132</v>
       </c>
       <c r="B97" s="34" t="s">
         <v>983</v>
@@ -10714,210 +10964,210 @@
       <c r="G98" s="34"/>
     </row>
     <row r="99" spans="1:7" ht="15" thickBot="1">
-      <c r="A99" s="37" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B99" s="39" t="s">
+      <c r="A99" s="38" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B99" s="40" t="s">
         <v>633</v>
       </c>
-      <c r="C99" s="39" t="s">
+      <c r="C99" s="40" t="s">
         <v>879</v>
       </c>
-      <c r="D99" s="39" t="s">
-        <v>1059</v>
-      </c>
-      <c r="E99" s="39" t="s">
+      <c r="D99" s="40" t="s">
         <v>1060</v>
       </c>
-      <c r="F99" s="39" t="s">
+      <c r="E99" s="40" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F99" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="G99" s="38" t="s">
-        <v>1061</v>
+      <c r="G99" s="39" t="s">
+        <v>1062</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15" thickBot="1">
-      <c r="A100" s="37" t="s">
-        <v>1133</v>
-      </c>
-      <c r="B100" s="39" t="s">
+      <c r="A100" s="38" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B100" s="40" t="s">
         <v>634</v>
       </c>
-      <c r="C100" s="39" t="s">
+      <c r="C100" s="40" t="s">
         <v>879</v>
       </c>
-      <c r="D100" s="39" t="s">
-        <v>1062</v>
-      </c>
-      <c r="E100" s="39" t="s">
+      <c r="D100" s="40" t="s">
         <v>1063</v>
       </c>
-      <c r="F100" s="39" t="s">
+      <c r="E100" s="40" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F100" s="40" t="s">
         <v>515</v>
       </c>
-      <c r="G100" s="38" t="s">
-        <v>1064</v>
+      <c r="G100" s="39" t="s">
+        <v>1065</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="15" thickBot="1">
-      <c r="A101" s="37" t="s">
-        <v>1134</v>
-      </c>
-      <c r="B101" s="39" t="s">
+      <c r="A101" s="38" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B101" s="40" t="s">
         <v>635</v>
       </c>
-      <c r="C101" s="39" t="s">
+      <c r="C101" s="40" t="s">
         <v>879</v>
       </c>
-      <c r="D101" s="39" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E101" s="39" t="s">
+      <c r="D101" s="40" t="s">
         <v>1066</v>
       </c>
-      <c r="F101" s="39" t="s">
+      <c r="E101" s="40" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F101" s="40" t="s">
         <v>381</v>
       </c>
-      <c r="G101" s="39" t="s">
-        <v>1067</v>
+      <c r="G101" s="40" t="s">
+        <v>1068</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15" thickBot="1">
-      <c r="A102" s="37" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B102" s="39" t="s">
+      <c r="A102" s="38" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B102" s="40" t="s">
         <v>636</v>
       </c>
-      <c r="C102" s="39" t="s">
+      <c r="C102" s="40" t="s">
         <v>879</v>
       </c>
-      <c r="D102" s="39" t="s">
-        <v>1068</v>
-      </c>
-      <c r="E102" s="39" t="s">
+      <c r="D102" s="40" t="s">
         <v>1069</v>
       </c>
-      <c r="F102" s="39" t="s">
+      <c r="E102" s="40" t="s">
         <v>1070</v>
       </c>
-      <c r="G102" s="38" t="s">
+      <c r="F102" s="40" t="s">
         <v>1071</v>
       </c>
+      <c r="G102" s="39" t="s">
+        <v>1072</v>
+      </c>
     </row>
     <row r="103" spans="1:7" ht="15" thickBot="1">
-      <c r="A103" s="37" t="s">
-        <v>1136</v>
-      </c>
-      <c r="B103" s="39" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C103" s="39" t="s">
+      <c r="A103" s="38" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B103" s="40" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C103" s="40" t="s">
         <v>879</v>
       </c>
-      <c r="D103" s="39" t="s">
-        <v>1073</v>
-      </c>
-      <c r="E103" s="39" t="s">
+      <c r="D103" s="40" t="s">
         <v>1074</v>
       </c>
-      <c r="F103" s="39" t="s">
+      <c r="E103" s="40" t="s">
         <v>1075</v>
       </c>
-      <c r="G103" s="38" t="s">
+      <c r="F103" s="40" t="s">
         <v>1076</v>
       </c>
+      <c r="G103" s="39" t="s">
+        <v>1077</v>
+      </c>
     </row>
     <row r="104" spans="1:7" ht="15" thickBot="1">
-      <c r="A104" s="37" t="s">
-        <v>1137</v>
-      </c>
-      <c r="B104" s="39" t="s">
+      <c r="A104" s="38" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B104" s="40" t="s">
         <v>637</v>
       </c>
-      <c r="C104" s="39" t="s">
+      <c r="C104" s="40" t="s">
         <v>879</v>
       </c>
-      <c r="D104" s="39" t="s">
-        <v>1077</v>
-      </c>
-      <c r="E104" s="39" t="s">
+      <c r="D104" s="40" t="s">
         <v>1078</v>
       </c>
-      <c r="F104" s="39" t="s">
+      <c r="E104" s="40" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F104" s="40" t="s">
         <v>381</v>
       </c>
-      <c r="G104" s="39" t="s">
+      <c r="G104" s="40" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" thickBot="1">
-      <c r="A105" s="37" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B105" s="39" t="s">
-        <v>1079</v>
-      </c>
-      <c r="C105" s="39" t="s">
+      <c r="A105" s="38" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B105" s="40" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C105" s="40" t="s">
         <v>879</v>
       </c>
-      <c r="D105" s="39" t="s">
-        <v>1080</v>
-      </c>
-      <c r="E105" s="39" t="s">
+      <c r="D105" s="40" t="s">
         <v>1081</v>
       </c>
-      <c r="F105" s="39" t="s">
+      <c r="E105" s="40" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F105" s="40" t="s">
         <v>988</v>
       </c>
-      <c r="G105" s="38" t="s">
-        <v>1082</v>
+      <c r="G105" s="39" t="s">
+        <v>1083</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" thickBot="1">
-      <c r="A106" s="37" t="s">
-        <v>1139</v>
-      </c>
-      <c r="B106" s="39" t="s">
+      <c r="A106" s="38" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B106" s="40" t="s">
         <v>638</v>
       </c>
-      <c r="C106" s="39" t="s">
+      <c r="C106" s="40" t="s">
         <v>879</v>
       </c>
-      <c r="D106" s="39" t="s">
-        <v>1083</v>
-      </c>
-      <c r="E106" s="39" t="s">
+      <c r="D106" s="40" t="s">
         <v>1084</v>
       </c>
-      <c r="F106" s="39" t="s">
+      <c r="E106" s="40" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F106" s="40" t="s">
         <v>526</v>
       </c>
-      <c r="G106" s="39" t="s">
-        <v>1085</v>
+      <c r="G106" s="40" t="s">
+        <v>1086</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15" thickBot="1">
-      <c r="A107" s="37" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B107" s="39" t="s">
+      <c r="A107" s="38" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B107" s="40" t="s">
         <v>639</v>
       </c>
-      <c r="C107" s="39" t="s">
+      <c r="C107" s="40" t="s">
         <v>879</v>
       </c>
-      <c r="D107" s="39" t="s">
-        <v>1086</v>
-      </c>
-      <c r="E107" s="39" t="s">
+      <c r="D107" s="40" t="s">
         <v>1087</v>
       </c>
-      <c r="F107" s="39" t="s">
+      <c r="E107" s="40" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F107" s="40" t="s">
         <v>526</v>
       </c>
-      <c r="G107" s="38" t="s">
-        <v>1088</v>
+      <c r="G107" s="39" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="15" thickBot="1">
@@ -10930,158 +11180,158 @@
       <c r="G108" s="34"/>
     </row>
     <row r="109" spans="1:7" ht="15" thickBot="1">
-      <c r="A109" s="37" t="s">
-        <v>1141</v>
+      <c r="A109" s="38" t="s">
+        <v>1142</v>
       </c>
       <c r="B109" s="34" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="C109" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D109" s="34" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="E109" s="34" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F109" s="34" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="G109" s="34" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="15" thickBot="1">
-      <c r="A110" s="37" t="s">
-        <v>1142</v>
+      <c r="A110" s="38" t="s">
+        <v>1143</v>
       </c>
       <c r="B110" s="34" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="C110" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D110" s="34" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E110" s="34" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F110" s="34" t="s">
         <v>1091</v>
-      </c>
-      <c r="E110" s="34" t="s">
-        <v>1066</v>
-      </c>
-      <c r="F110" s="34" t="s">
-        <v>1090</v>
       </c>
       <c r="G110" s="34" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="15" thickBot="1">
-      <c r="A111" s="37" t="s">
-        <v>1143</v>
+      <c r="A111" s="38" t="s">
+        <v>1144</v>
       </c>
       <c r="B111" s="34" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="C111" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D111" s="34" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E111" s="34" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F111" s="34" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="G111" s="34" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="15" thickBot="1">
-      <c r="A112" s="37" t="s">
-        <v>1144</v>
+      <c r="A112" s="38" t="s">
+        <v>1145</v>
       </c>
       <c r="B112" s="34" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="C112" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D112" s="34" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="E112" s="34" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F112" s="34" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="G112" s="34" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="15" thickBot="1">
-      <c r="A113" s="37" t="s">
-        <v>1145</v>
+      <c r="A113" s="38" t="s">
+        <v>1146</v>
       </c>
       <c r="B113" s="34" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C113" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D113" s="34" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="E113" s="34" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F113" s="34" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="G113" s="34" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="15" thickBot="1">
-      <c r="A114" s="37" t="s">
-        <v>1146</v>
+      <c r="A114" s="38" t="s">
+        <v>1147</v>
       </c>
       <c r="B114" s="34" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="C114" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D114" s="34" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="E114" s="34" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F114" s="34" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G114" s="34" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="15" thickBot="1">
-      <c r="A115" s="37" t="s">
-        <v>1147</v>
+      <c r="A115" s="38" t="s">
+        <v>1148</v>
       </c>
       <c r="B115" s="34" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="C115" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D115" s="34" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="E115" s="34" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F115" s="36">
         <v>12345678</v>
@@ -11091,43 +11341,43 @@
       </c>
     </row>
     <row r="116" spans="1:7" ht="15" thickBot="1">
-      <c r="A116" s="37" t="s">
-        <v>1148</v>
+      <c r="A116" s="38" t="s">
+        <v>1149</v>
       </c>
       <c r="B116" s="34" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="C116" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D116" s="34" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="E116" s="34" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F116" s="34" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="G116" s="34" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15" thickBot="1">
-      <c r="A117" s="37" t="s">
-        <v>1149</v>
+      <c r="A117" s="38" t="s">
+        <v>1150</v>
       </c>
       <c r="B117" s="34" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="C117" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D117" s="34" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="E117" s="34" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F117" s="34"/>
       <c r="G117" s="34" t="s">
@@ -11135,20 +11385,20 @@
       </c>
     </row>
     <row r="118" spans="1:7" ht="15" thickBot="1">
-      <c r="A118" s="37" t="s">
-        <v>1150</v>
+      <c r="A118" s="38" t="s">
+        <v>1151</v>
       </c>
       <c r="B118" s="34" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C118" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D118" s="34" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E118" s="34" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F118" s="34" t="s">
         <v>26</v>
@@ -11158,215 +11408,215 @@
       </c>
     </row>
     <row r="119" spans="1:7" ht="15" thickBot="1">
-      <c r="A119" s="37" t="s">
-        <v>1151</v>
+      <c r="A119" s="38" t="s">
+        <v>1152</v>
       </c>
       <c r="B119" s="34" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C119" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D119" s="34" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="E119" s="34" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F119" s="34" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="G119" s="34" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="15" thickBot="1">
-      <c r="A120" s="37" t="s">
-        <v>1152</v>
+      <c r="A120" s="38" t="s">
+        <v>1153</v>
       </c>
       <c r="B120" s="34" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="C120" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D120" s="34" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="E120" s="34" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F120" s="34" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G120" s="34" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15" thickBot="1">
-      <c r="A121" s="37" t="s">
-        <v>1153</v>
+      <c r="A121" s="38" t="s">
+        <v>1154</v>
       </c>
       <c r="B121" s="34" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="C121" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D121" s="34" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="E121" s="34" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F121" s="34" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="G121" s="34" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15" thickBot="1">
-      <c r="A122" s="37" t="s">
-        <v>1154</v>
+      <c r="A122" s="38" t="s">
+        <v>1155</v>
       </c>
       <c r="B122" s="34" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="C122" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D122" s="34" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="E122" s="34" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F122" s="34" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="G122" s="34" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15" thickBot="1">
-      <c r="A123" s="37" t="s">
-        <v>1155</v>
+      <c r="A123" s="38" t="s">
+        <v>1156</v>
       </c>
       <c r="B123" s="34" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="C123" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D123" s="34" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="E123" s="34" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F123" s="34" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="G123" s="34" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="15" thickBot="1">
-      <c r="A124" s="37" t="s">
-        <v>1156</v>
+      <c r="A124" s="38" t="s">
+        <v>1157</v>
       </c>
       <c r="B124" s="34" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="C124" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D124" s="34" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="E124" s="34" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F124" s="34" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="G124" s="34" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="15" thickBot="1">
-      <c r="A125" s="37" t="s">
-        <v>1157</v>
+      <c r="A125" s="38" t="s">
+        <v>1158</v>
       </c>
       <c r="B125" s="34" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="C125" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D125" s="34" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="E125" s="34" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F125" s="34" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="G125" s="34" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="15" thickBot="1">
-      <c r="A126" s="37" t="s">
-        <v>1158</v>
+      <c r="A126" s="38" t="s">
+        <v>1159</v>
       </c>
       <c r="B126" s="34" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="C126" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D126" s="34" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="E126" s="34" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F126" s="34" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="G126" s="34" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="15" thickBot="1">
-      <c r="A127" s="37" t="s">
-        <v>1159</v>
+      <c r="A127" s="38" t="s">
+        <v>1160</v>
       </c>
       <c r="B127" s="34" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="C127" s="34" t="s">
         <v>879</v>
       </c>
       <c r="D127" s="34" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="E127" s="34" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F127" s="34" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="G127" s="34" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="129" spans="1:7">
-      <c r="A129" s="37" t="s">
-        <v>1159</v>
+      <c r="A129" s="38" t="s">
+        <v>1160</v>
       </c>
       <c r="B129" t="s">
         <v>640</v>
@@ -11388,8 +11638,8 @@
       </c>
     </row>
     <row r="130" spans="1:7">
-      <c r="A130" s="37" t="s">
-        <v>1160</v>
+      <c r="A130" s="38" t="s">
+        <v>1161</v>
       </c>
       <c r="B130" t="s">
         <v>642</v>
@@ -11411,8 +11661,8 @@
       </c>
     </row>
     <row r="131" spans="1:7">
-      <c r="A131" s="37" t="s">
-        <v>1161</v>
+      <c r="A131" s="38" t="s">
+        <v>1162</v>
       </c>
       <c r="B131" t="s">
         <v>647</v>
@@ -11434,8 +11684,8 @@
       </c>
     </row>
     <row r="132" spans="1:7">
-      <c r="A132" s="37" t="s">
-        <v>1162</v>
+      <c r="A132" s="38" t="s">
+        <v>1163</v>
       </c>
       <c r="B132" t="s">
         <v>651</v>
@@ -11457,8 +11707,8 @@
       </c>
     </row>
     <row r="134" spans="1:7">
-      <c r="A134" s="37" t="s">
-        <v>1163</v>
+      <c r="A134" s="38" t="s">
+        <v>1164</v>
       </c>
       <c r="B134" t="s">
         <v>655</v>
@@ -11480,8 +11730,8 @@
       </c>
     </row>
     <row r="135" spans="1:7">
-      <c r="A135" s="37" t="s">
-        <v>1164</v>
+      <c r="A135" s="38" t="s">
+        <v>1165</v>
       </c>
       <c r="B135" t="s">
         <v>657</v>
@@ -11503,8 +11753,8 @@
       </c>
     </row>
     <row r="136" spans="1:7">
-      <c r="A136" s="37" t="s">
-        <v>1165</v>
+      <c r="A136" s="38" t="s">
+        <v>1166</v>
       </c>
       <c r="B136" t="s">
         <v>660</v>
@@ -11526,8 +11776,8 @@
       </c>
     </row>
     <row r="137" spans="1:7">
-      <c r="A137" s="37" t="s">
-        <v>1166</v>
+      <c r="A137" s="38" t="s">
+        <v>1167</v>
       </c>
       <c r="B137" t="s">
         <v>663</v>
@@ -11549,8 +11799,8 @@
       </c>
     </row>
     <row r="138" spans="1:7">
-      <c r="A138" s="37" t="s">
-        <v>1167</v>
+      <c r="A138" s="38" t="s">
+        <v>1168</v>
       </c>
       <c r="B138" t="s">
         <v>666</v>
@@ -11572,8 +11822,8 @@
       </c>
     </row>
     <row r="139" spans="1:7">
-      <c r="A139" s="37" t="s">
-        <v>1168</v>
+      <c r="A139" s="38" t="s">
+        <v>1169</v>
       </c>
       <c r="B139" t="s">
         <v>669</v>
@@ -11595,8 +11845,8 @@
       </c>
     </row>
     <row r="140" spans="1:7">
-      <c r="A140" s="37" t="s">
-        <v>1169</v>
+      <c r="A140" s="38" t="s">
+        <v>1170</v>
       </c>
       <c r="B140" t="s">
         <v>672</v>
@@ -11618,8 +11868,8 @@
       </c>
     </row>
     <row r="141" spans="1:7">
-      <c r="A141" s="37" t="s">
-        <v>1170</v>
+      <c r="A141" s="38" t="s">
+        <v>1171</v>
       </c>
       <c r="B141" t="s">
         <v>676</v>
@@ -11641,8 +11891,8 @@
       </c>
     </row>
     <row r="142" spans="1:7">
-      <c r="A142" s="37" t="s">
-        <v>1171</v>
+      <c r="A142" s="38" t="s">
+        <v>1172</v>
       </c>
       <c r="B142" t="s">
         <v>679</v>
@@ -11664,8 +11914,8 @@
       </c>
     </row>
     <row r="143" spans="1:7">
-      <c r="A143" s="37" t="s">
-        <v>1172</v>
+      <c r="A143" s="38" t="s">
+        <v>1173</v>
       </c>
       <c r="B143" t="s">
         <v>683</v>
@@ -11687,8 +11937,8 @@
       </c>
     </row>
     <row r="144" spans="1:7">
-      <c r="A144" s="37" t="s">
-        <v>1173</v>
+      <c r="A144" s="38" t="s">
+        <v>1174</v>
       </c>
       <c r="B144" t="s">
         <v>686</v>
@@ -11710,8 +11960,8 @@
       </c>
     </row>
     <row r="145" spans="1:7">
-      <c r="A145" s="37" t="s">
-        <v>1174</v>
+      <c r="A145" s="38" t="s">
+        <v>1175</v>
       </c>
       <c r="B145" t="s">
         <v>690</v>
@@ -11733,8 +11983,8 @@
       </c>
     </row>
     <row r="146" spans="1:7">
-      <c r="A146" s="37" t="s">
-        <v>1175</v>
+      <c r="A146" s="38" t="s">
+        <v>1176</v>
       </c>
       <c r="B146" t="s">
         <v>694</v>
@@ -11756,8 +12006,8 @@
       </c>
     </row>
     <row r="147" spans="1:7">
-      <c r="A147" s="37" t="s">
-        <v>1176</v>
+      <c r="A147" s="38" t="s">
+        <v>1177</v>
       </c>
       <c r="B147" t="s">
         <v>696</v>
@@ -11779,8 +12029,8 @@
       </c>
     </row>
     <row r="148" spans="1:7">
-      <c r="A148" s="37" t="s">
-        <v>1177</v>
+      <c r="A148" s="38" t="s">
+        <v>1178</v>
       </c>
       <c r="B148" t="s">
         <v>698</v>
@@ -11802,8 +12052,8 @@
       </c>
     </row>
     <row r="149" spans="1:7">
-      <c r="A149" s="37" t="s">
-        <v>1178</v>
+      <c r="A149" s="38" t="s">
+        <v>1179</v>
       </c>
       <c r="B149" t="s">
         <v>700</v>
@@ -11825,8 +12075,8 @@
       </c>
     </row>
     <row r="150" spans="1:7">
-      <c r="A150" s="37" t="s">
-        <v>1179</v>
+      <c r="A150" s="38" t="s">
+        <v>1180</v>
       </c>
       <c r="B150" t="s">
         <v>704</v>
@@ -11848,8 +12098,8 @@
       </c>
     </row>
     <row r="151" spans="1:7">
-      <c r="A151" s="37" t="s">
-        <v>1180</v>
+      <c r="A151" s="38" t="s">
+        <v>1181</v>
       </c>
       <c r="B151" t="s">
         <v>707</v>
@@ -12957,4 +13207,368 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7C66A06-D3DD-4B57-9443-1D7FCDC0F451}">
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="17.77734375" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="56.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="184.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="110.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15" thickBot="1">
+      <c r="A1" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C1" s="34"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+    </row>
+    <row r="2" spans="1:10" ht="15" thickBot="1">
+      <c r="A2" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C2" s="34"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+    </row>
+    <row r="3" spans="1:10" ht="15" thickBot="1">
+      <c r="A3" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="34"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+    </row>
+    <row r="4" spans="1:10" ht="15" thickBot="1">
+      <c r="A4" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C4" s="34"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+    </row>
+    <row r="7" spans="1:10" ht="15" thickBot="1">
+      <c r="A7" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15" thickBot="1">
+      <c r="A8" s="45" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F8" s="43" t="s">
+        <v>1281</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H8" s="34"/>
+    </row>
+    <row r="9" spans="1:10" ht="15" thickBot="1">
+      <c r="A9" s="45" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>1286</v>
+      </c>
+      <c r="F9" s="43" t="s">
+        <v>1287</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>1288</v>
+      </c>
+      <c r="H9" s="34"/>
+    </row>
+    <row r="10" spans="1:10" ht="15" thickBot="1">
+      <c r="A10" s="45" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>1292</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>1293</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>1294</v>
+      </c>
+      <c r="H10" s="34"/>
+    </row>
+    <row r="11" spans="1:10" ht="15" thickBot="1">
+      <c r="A11" s="45" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>989</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>1299</v>
+      </c>
+      <c r="H11" s="34"/>
+    </row>
+    <row r="12" spans="1:10" ht="15" thickBot="1">
+      <c r="A12" s="45" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F12" s="43" t="s">
+        <v>1304</v>
+      </c>
+      <c r="G12" s="41" t="s">
+        <v>1305</v>
+      </c>
+      <c r="H12" s="34"/>
+    </row>
+    <row r="13" spans="1:10" ht="15" thickBot="1">
+      <c r="A13" s="45" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B13" s="43" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F13" s="43" t="s">
+        <v>681</v>
+      </c>
+      <c r="G13" s="41" t="s">
+        <v>1310</v>
+      </c>
+      <c r="H13" s="34"/>
+    </row>
+    <row r="14" spans="1:10" ht="15" thickBot="1">
+      <c r="A14" s="45" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B14" s="43" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>1313</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>1314</v>
+      </c>
+      <c r="F14" s="43" t="s">
+        <v>1315</v>
+      </c>
+      <c r="G14" s="41" t="s">
+        <v>1316</v>
+      </c>
+      <c r="H14" s="34"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" thickBot="1">
+      <c r="A15" s="45" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B15" s="43" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>1319</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>1320</v>
+      </c>
+      <c r="F15" s="43" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G15" s="41" t="s">
+        <v>1322</v>
+      </c>
+      <c r="H15" s="34"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" thickBot="1">
+      <c r="A16" s="45" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>1326</v>
+      </c>
+      <c r="F16" s="43" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G16" s="41" t="s">
+        <v>1328</v>
+      </c>
+      <c r="H16" s="34"/>
+    </row>
+    <row r="17" spans="1:8" ht="15" thickBot="1">
+      <c r="A17" s="45" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>1332</v>
+      </c>
+      <c r="F17" s="43" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G17" s="41" t="s">
+        <v>1334</v>
+      </c>
+      <c r="H17" s="34"/>
+    </row>
+    <row r="19" spans="1:8" ht="15" thickBot="1"/>
+    <row r="20" spans="1:8" ht="15" thickBot="1">
+      <c r="A20" s="23" t="s">
+        <v>470</v>
+      </c>
+      <c r="B20" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15" thickBot="1">
+      <c r="A21" s="23" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15" thickBot="1">
+      <c r="A22" s="23" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15" thickBot="1">
+      <c r="A23" s="23" t="s">
+        <v>474</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>